--- a/table/resources/sample/common/warehouse.xlsx
+++ b/table/resources/sample/common/warehouse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -1922,10 +1922,10 @@
         <v>1</v>
       </c>
       <c r="F20" s="1">
-        <v>100</v>
+        <v>-1</v>
       </c>
       <c r="G20" s="1">
-        <v>5000000</v>
+        <v>-1</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
@@ -1955,10 +1955,10 @@
         <v>2</v>
       </c>
       <c r="F21" s="1">
-        <v>10000</v>
+        <v>-1</v>
       </c>
       <c r="G21" s="1">
-        <v>500000000</v>
+        <v>-1</v>
       </c>
       <c r="H21" s="1">
         <v>30</v>
@@ -1988,7 +1988,7 @@
         <v>3</v>
       </c>
       <c r="F22" s="1">
-        <v>1000000</v>
+        <v>-1</v>
       </c>
       <c r="G22" s="1">
         <v>-1</v>

--- a/table/resources/sample/common/warehouse.xlsx
+++ b/table/resources/sample/common/warehouse.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375" tabRatio="794"/>
+    <workbookView windowWidth="27945" windowHeight="12375" tabRatio="794"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse" sheetId="42" r:id="rId1"/>
@@ -32,6 +32,29 @@
     <author>Administrator</author>
   </authors>
   <commentList>
+    <comment ref="E1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1-9 倍场ID
+10 需要付费开启得房间游戏</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="F1" authorId="0">
       <text>
         <r>
@@ -86,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="43">
   <si>
     <t>sid</t>
   </si>
@@ -112,6 +135,9 @@
     <t>最少保留房间数量：无人后间隔X秒删除</t>
   </si>
   <si>
+    <t>倍场显示默认押注</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -127,6 +153,9 @@
     <t>gameID</t>
   </si>
   <si>
+    <t>roomType</t>
+  </si>
+  <si>
     <t>enterLimit</t>
   </si>
   <si>
@@ -142,6 +171,9 @@
     <t>RoomDeletion_Solution</t>
   </si>
   <si>
+    <t>BetShow</t>
+  </si>
+  <si>
     <t>金矿大亨</t>
   </si>
   <si>
@@ -173,6 +205,9 @@
   </si>
   <si>
     <t>百家乐</t>
+  </si>
+  <si>
+    <t>4:3600</t>
   </si>
   <si>
     <t>三个骰子</t>
@@ -409,12 +444,12 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1291,7 +1326,7 @@
     <col min="1" max="2" width="9.375" style="1"/>
     <col min="3" max="6" width="9" style="1"/>
     <col min="7" max="7" width="11.25" style="1" customWidth="1"/>
-    <col min="8" max="8" width="9" style="1"/>
+    <col min="8" max="8" width="10.625" style="1" customWidth="1"/>
     <col min="9" max="9" width="29.7" style="1" customWidth="1"/>
     <col min="10" max="10" width="37.125" style="1" customWidth="1"/>
     <col min="11" max="11" width="17.2166666666667" customWidth="1"/>
@@ -1300,7 +1335,7 @@
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.5" spans="1:10">
+    <row r="1" ht="16.5" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1331,57 +1366,71 @@
       <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:10">
+      <c r="K1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:11">
       <c r="A2" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
+      <c r="E2" s="6" t="s">
+        <v>9</v>
+      </c>
       <c r="F2" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:10">
+    </row>
+    <row r="3" ht="16.5" spans="1:11">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>14</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:10">
+        <v>19</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="1:11">
       <c r="A5" s="1">
         <f>B5*10+E5</f>
         <v>1001001</v>
@@ -1390,10 +1439,10 @@
         <v>100100</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E5" s="1">
         <v>1</v>
@@ -1408,13 +1457,16 @@
         <v>0</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:10">
+        <v>24</v>
+      </c>
+      <c r="K5">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:11">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A51" si="0">B6*10+E6</f>
         <v>1001002</v>
@@ -1427,7 +1479,7 @@
         <v>金矿大亨</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E6" s="1">
         <v>2</v>
@@ -1439,16 +1491,19 @@
         <v>-1</v>
       </c>
       <c r="H6" s="1">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:10">
+        <v>24</v>
+      </c>
+      <c r="K6">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:11">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>1001003</v>
@@ -1461,7 +1516,7 @@
         <v>金矿大亨</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E7" s="1">
         <v>3</v>
@@ -1473,16 +1528,19 @@
         <v>-1</v>
       </c>
       <c r="H7" s="1">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:10">
+        <v>24</v>
+      </c>
+      <c r="K7">
+        <v>10000000</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:11">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>2001001</v>
@@ -1491,10 +1549,10 @@
         <v>200100</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E8" s="1">
         <v>1</v>
@@ -1506,16 +1564,19 @@
         <v>5000000</v>
       </c>
       <c r="H8" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:10">
+        <v>24</v>
+      </c>
+      <c r="K8">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:11">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>2001002</v>
@@ -1528,7 +1589,7 @@
         <v>红黑大战</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E9" s="1">
         <v>2</v>
@@ -1540,16 +1601,19 @@
         <v>500000000</v>
       </c>
       <c r="H9" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" ht="16.5" spans="1:10">
+        <v>24</v>
+      </c>
+      <c r="K9">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="1:11">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>2001003</v>
@@ -1562,7 +1626,7 @@
         <v>红黑大战</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E10" s="1">
         <v>3</v>
@@ -1574,16 +1638,19 @@
         <v>-1</v>
       </c>
       <c r="H10" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:10">
+        <v>24</v>
+      </c>
+      <c r="K10">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:11">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>2001011</v>
@@ -1592,10 +1659,10 @@
         <v>200101</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E11" s="1">
         <v>1</v>
@@ -1607,13 +1674,16 @@
         <v>5000000</v>
       </c>
       <c r="H11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="K11">
+        <v>500</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" ht="16.5" spans="1:13">
@@ -1629,7 +1699,7 @@
         <v>龙虎斗</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E12" s="1">
         <v>2</v>
@@ -1641,15 +1711,17 @@
         <v>500000000</v>
       </c>
       <c r="H12" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K12"/>
+        <v>24</v>
+      </c>
+      <c r="K12">
+        <v>20000</v>
+      </c>
       <c r="L12"/>
       <c r="M12"/>
     </row>
@@ -1666,7 +1738,7 @@
         <v>龙虎斗</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E13" s="1">
         <v>3</v>
@@ -1678,19 +1750,21 @@
         <v>-1</v>
       </c>
       <c r="H13" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K13"/>
+        <v>24</v>
+      </c>
+      <c r="K13">
+        <v>2000000</v>
+      </c>
       <c r="L13"/>
       <c r="M13"/>
     </row>
-    <row r="14" ht="16.5" spans="1:10">
+    <row r="14" ht="16.5" spans="1:11">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>2003001</v>
@@ -1699,10 +1773,10 @@
         <v>200300</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E14" s="1">
         <v>1</v>
@@ -1714,13 +1788,16 @@
         <v>5000000</v>
       </c>
       <c r="H14" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="K14">
+        <v>500</v>
       </c>
     </row>
     <row r="15" s="1" customFormat="1" ht="16.5" spans="1:13">
@@ -1736,7 +1813,7 @@
         <v>飞禽走兽</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E15" s="1">
         <v>2</v>
@@ -1748,15 +1825,17 @@
         <v>500000000</v>
       </c>
       <c r="H15" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15"/>
+        <v>24</v>
+      </c>
+      <c r="K15">
+        <v>20000</v>
+      </c>
       <c r="L15"/>
       <c r="M15"/>
     </row>
@@ -1773,7 +1852,7 @@
         <v>飞禽走兽</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E16" s="1">
         <v>3</v>
@@ -1785,19 +1864,21 @@
         <v>-1</v>
       </c>
       <c r="H16" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16"/>
+        <v>24</v>
+      </c>
+      <c r="K16">
+        <v>2000000</v>
+      </c>
       <c r="L16"/>
       <c r="M16"/>
     </row>
-    <row r="17" ht="16.5" spans="1:10">
+    <row r="17" ht="16.5" spans="1:11">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>2004001</v>
@@ -1806,10 +1887,10 @@
         <v>200400</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E17" s="1">
         <v>1</v>
@@ -1821,13 +1902,16 @@
         <v>5000000</v>
       </c>
       <c r="H17" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="K17">
+        <v>500</v>
       </c>
     </row>
     <row r="18" s="1" customFormat="1" ht="16.5" spans="1:13">
@@ -1843,7 +1927,7 @@
         <v>豪车俱乐部</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E18" s="1">
         <v>2</v>
@@ -1855,15 +1939,17 @@
         <v>500000000</v>
       </c>
       <c r="H18" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J18" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K18"/>
+        <v>24</v>
+      </c>
+      <c r="K18">
+        <v>20000</v>
+      </c>
       <c r="L18"/>
       <c r="M18"/>
     </row>
@@ -1880,7 +1966,7 @@
         <v>豪车俱乐部</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E19" s="1">
         <v>3</v>
@@ -1892,19 +1978,21 @@
         <v>-1</v>
       </c>
       <c r="H19" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K19"/>
+        <v>24</v>
+      </c>
+      <c r="K19">
+        <v>2000000</v>
+      </c>
       <c r="L19"/>
       <c r="M19"/>
     </row>
-    <row r="20" ht="16.5" spans="1:10">
+    <row r="20" ht="16.5" spans="1:11">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>2005001</v>
@@ -1913,31 +2001,34 @@
         <v>200500</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E20" s="1">
         <v>1</v>
       </c>
       <c r="F20" s="1">
-        <v>-1</v>
+        <v>100</v>
       </c>
       <c r="G20" s="1">
-        <v>-1</v>
+        <v>5000000</v>
       </c>
       <c r="H20" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:10">
+        <v>32</v>
+      </c>
+      <c r="K20">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:11">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>2005002</v>
@@ -1946,31 +2037,34 @@
         <v>200500</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E21" s="1">
         <v>2</v>
       </c>
       <c r="F21" s="1">
-        <v>-1</v>
+        <v>10000</v>
       </c>
       <c r="G21" s="1">
-        <v>-1</v>
+        <v>500000000</v>
       </c>
       <c r="H21" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" ht="16.5" spans="1:10">
+        <v>32</v>
+      </c>
+      <c r="K21">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="22" ht="16.5" spans="1:11">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>2005003</v>
@@ -1979,31 +2073,34 @@
         <v>200500</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E22" s="1">
         <v>3</v>
       </c>
       <c r="F22" s="1">
-        <v>-1</v>
+        <v>1000000</v>
       </c>
       <c r="G22" s="1">
         <v>-1</v>
       </c>
       <c r="H22" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" ht="16.5" spans="1:10">
+        <v>32</v>
+      </c>
+      <c r="K22">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="1:11">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>2006001</v>
@@ -2012,10 +2109,10 @@
         <v>200600</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E23" s="1">
         <v>1</v>
@@ -2027,13 +2124,16 @@
         <v>5000000</v>
       </c>
       <c r="H23" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="K23">
+        <v>500</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" ht="16.5" spans="1:13">
@@ -2049,7 +2149,7 @@
         <v>三个骰子</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E24" s="1">
         <v>2</v>
@@ -2061,15 +2161,17 @@
         <v>500000000</v>
       </c>
       <c r="H24" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K24"/>
+        <v>24</v>
+      </c>
+      <c r="K24">
+        <v>20000</v>
+      </c>
       <c r="L24"/>
       <c r="M24"/>
     </row>
@@ -2086,7 +2188,7 @@
         <v>三个骰子</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E25" s="1">
         <v>3</v>
@@ -2098,19 +2200,21 @@
         <v>-1</v>
       </c>
       <c r="H25" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J25" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K25"/>
+        <v>24</v>
+      </c>
+      <c r="K25">
+        <v>2000000</v>
+      </c>
       <c r="L25"/>
       <c r="M25"/>
     </row>
-    <row r="26" ht="16.5" spans="1:10">
+    <row r="26" ht="16.5" spans="1:11">
       <c r="A26" s="1">
         <f t="shared" si="0"/>
         <v>2007001</v>
@@ -2119,10 +2223,10 @@
         <v>200700</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E26" s="1">
         <v>1</v>
@@ -2134,13 +2238,16 @@
         <v>5000000</v>
       </c>
       <c r="H26" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J26" s="12" t="s">
-        <v>21</v>
+        <v>24</v>
+      </c>
+      <c r="K26">
+        <v>500</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" ht="16.5" spans="1:13">
@@ -2156,7 +2263,7 @@
         <v>色碟</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E27" s="1">
         <v>2</v>
@@ -2168,15 +2275,17 @@
         <v>500000000</v>
       </c>
       <c r="H27" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J27" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K27"/>
+        <v>24</v>
+      </c>
+      <c r="K27">
+        <v>20000</v>
+      </c>
       <c r="L27"/>
       <c r="M27"/>
     </row>
@@ -2193,7 +2302,7 @@
         <v>色碟</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E28" s="1">
         <v>3</v>
@@ -2205,15 +2314,17 @@
         <v>-1</v>
       </c>
       <c r="H28" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J28" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K28"/>
+        <v>24</v>
+      </c>
+      <c r="K28">
+        <v>2000000</v>
+      </c>
       <c r="L28"/>
       <c r="M28"/>
     </row>
@@ -2226,10 +2337,10 @@
         <v>200800</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E29" s="1">
         <v>1</v>
@@ -2241,15 +2352,17 @@
         <v>5000000</v>
       </c>
       <c r="H29" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J29" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K29"/>
+        <v>24</v>
+      </c>
+      <c r="K29">
+        <v>500</v>
+      </c>
       <c r="L29"/>
       <c r="M29"/>
     </row>
@@ -2262,10 +2375,10 @@
         <v>200800</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E30" s="1">
         <v>2</v>
@@ -2277,15 +2390,17 @@
         <v>500000000</v>
       </c>
       <c r="H30" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J30" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K30"/>
+        <v>24</v>
+      </c>
+      <c r="K30">
+        <v>20000</v>
+      </c>
       <c r="L30"/>
       <c r="M30"/>
     </row>
@@ -2298,10 +2413,10 @@
         <v>200800</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E31" s="1">
         <v>3</v>
@@ -2313,19 +2428,21 @@
         <v>-1</v>
       </c>
       <c r="H31" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J31" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K31"/>
+        <v>24</v>
+      </c>
+      <c r="K31">
+        <v>2000000</v>
+      </c>
       <c r="L31"/>
       <c r="M31"/>
     </row>
-    <row r="32" ht="16.5" spans="1:10">
+    <row r="32" ht="16.5" spans="1:11">
       <c r="A32" s="1">
         <f t="shared" si="0"/>
         <v>2009001</v>
@@ -2334,10 +2451,10 @@
         <v>200900</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E32" s="1">
         <v>1</v>
@@ -2349,16 +2466,19 @@
         <v>5000000</v>
       </c>
       <c r="H32" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J32" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" ht="16.5" spans="1:10">
+        <v>24</v>
+      </c>
+      <c r="K32">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="1:11">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>2009002</v>
@@ -2371,7 +2491,7 @@
         <v>鱼虾蟹</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E33" s="1">
         <v>2</v>
@@ -2383,16 +2503,19 @@
         <v>500000000</v>
       </c>
       <c r="H33" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J33" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" ht="16.5" spans="1:10">
+        <v>24</v>
+      </c>
+      <c r="K33">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" spans="1:11">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>2009003</v>
@@ -2405,7 +2528,7 @@
         <v>鱼虾蟹</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E34" s="1">
         <v>3</v>
@@ -2417,16 +2540,19 @@
         <v>-1</v>
       </c>
       <c r="H34" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J34" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" ht="16.5" spans="1:10">
+        <v>24</v>
+      </c>
+      <c r="K34">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="1:11">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>2010001</v>
@@ -2435,10 +2561,10 @@
         <v>201000</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E35" s="1">
         <v>1</v>
@@ -2450,16 +2576,19 @@
         <v>5000000</v>
       </c>
       <c r="H35" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J35" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="36" ht="16.5" spans="1:10">
+        <v>24</v>
+      </c>
+      <c r="K35">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" spans="1:11">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>2010002</v>
@@ -2468,10 +2597,10 @@
         <v>201000</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E36" s="1">
         <v>2</v>
@@ -2483,16 +2612,19 @@
         <v>500000000</v>
       </c>
       <c r="H36" s="1">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J36" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="37" ht="16.5" spans="1:10">
+        <v>24</v>
+      </c>
+      <c r="K36">
+        <v>20000</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" spans="1:11">
       <c r="A37" s="1">
         <f t="shared" si="0"/>
         <v>2010003</v>
@@ -2501,10 +2633,10 @@
         <v>201000</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E37" s="1">
         <v>3</v>
@@ -2516,16 +2648,19 @@
         <v>-1</v>
       </c>
       <c r="H37" s="1">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J37" s="12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="38" ht="16.5" spans="1:10">
+        <v>24</v>
+      </c>
+      <c r="K37">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="38" ht="16.5" spans="1:11">
       <c r="A38" s="1">
         <f t="shared" si="0"/>
         <v>3001001</v>
@@ -2534,10 +2669,10 @@
         <v>300100</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E38" s="1">
         <v>1</v>
@@ -2548,11 +2683,17 @@
       <c r="G38" s="1">
         <v>-1</v>
       </c>
+      <c r="H38" s="1">
+        <v>0</v>
+      </c>
       <c r="I38" s="13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J38" s="13" t="s">
-        <v>36</v>
+        <v>40</v>
+      </c>
+      <c r="K38">
+        <v>500</v>
       </c>
     </row>
     <row r="39" s="1" customFormat="1" ht="16.5" spans="1:13">
@@ -2564,10 +2705,10 @@
         <v>300100</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E39" s="1">
         <v>2</v>
@@ -2578,14 +2719,18 @@
       <c r="G39" s="1">
         <v>-1</v>
       </c>
-      <c r="H39" s="1"/>
+      <c r="H39" s="1">
+        <v>0</v>
+      </c>
       <c r="I39" s="13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J39" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="K39"/>
+        <v>40</v>
+      </c>
+      <c r="K39">
+        <v>20000</v>
+      </c>
       <c r="L39"/>
       <c r="M39"/>
     </row>
@@ -2598,10 +2743,10 @@
         <v>300100</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E40" s="1">
         <v>3</v>
@@ -2612,14 +2757,18 @@
       <c r="G40" s="1">
         <v>-1</v>
       </c>
-      <c r="H40" s="1"/>
+      <c r="H40" s="1">
+        <v>0</v>
+      </c>
       <c r="I40" s="13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J40" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="K40"/>
+        <v>40</v>
+      </c>
+      <c r="K40">
+        <v>2000000</v>
+      </c>
       <c r="L40"/>
       <c r="M40"/>
     </row>
@@ -2632,10 +2781,10 @@
         <v>100100</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E41" s="10">
         <v>10</v>
@@ -2646,16 +2795,18 @@
       <c r="G41" s="10">
         <v>-1</v>
       </c>
-      <c r="H41" s="10">
-        <v>1</v>
+      <c r="H41" s="1">
+        <v>0</v>
       </c>
       <c r="I41" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J41" s="10">
         <v>1</v>
       </c>
-      <c r="K41"/>
+      <c r="K41">
+        <v>100</v>
+      </c>
       <c r="L41"/>
       <c r="M41"/>
     </row>
@@ -2668,10 +2819,10 @@
         <v>200100</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E42" s="10">
         <v>10</v>
@@ -2682,16 +2833,18 @@
       <c r="G42" s="10">
         <v>-1</v>
       </c>
-      <c r="H42" s="10">
-        <v>30</v>
+      <c r="H42" s="1">
+        <v>0</v>
       </c>
       <c r="I42" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J42" s="10">
         <v>1</v>
       </c>
-      <c r="K42"/>
+      <c r="K42">
+        <v>100</v>
+      </c>
       <c r="L42"/>
       <c r="M42"/>
     </row>
@@ -2704,10 +2857,10 @@
         <v>200101</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E43" s="10">
         <v>10</v>
@@ -2718,20 +2871,22 @@
       <c r="G43" s="10">
         <v>-1</v>
       </c>
-      <c r="H43" s="10">
-        <v>50</v>
+      <c r="H43" s="1">
+        <v>0</v>
       </c>
       <c r="I43" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J43" s="10">
         <v>1</v>
       </c>
-      <c r="K43"/>
+      <c r="K43">
+        <v>100</v>
+      </c>
       <c r="L43"/>
       <c r="M43"/>
     </row>
-    <row r="44" ht="16.5" spans="1:10">
+    <row r="44" ht="16.5" spans="1:11">
       <c r="A44" s="1">
         <f t="shared" si="0"/>
         <v>2003010</v>
@@ -2740,10 +2895,10 @@
         <v>200300</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E44" s="10">
         <v>10</v>
@@ -2754,17 +2909,20 @@
       <c r="G44" s="10">
         <v>-1</v>
       </c>
-      <c r="H44" s="10">
-        <v>1</v>
+      <c r="H44" s="1">
+        <v>0</v>
       </c>
       <c r="I44" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J44" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" ht="16.5" spans="1:10">
+      <c r="K44">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:11">
       <c r="A45" s="1">
         <f t="shared" si="0"/>
         <v>2004010</v>
@@ -2773,10 +2931,10 @@
         <v>200400</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E45" s="10">
         <v>10</v>
@@ -2787,17 +2945,20 @@
       <c r="G45" s="10">
         <v>-1</v>
       </c>
-      <c r="H45" s="10">
-        <v>30</v>
+      <c r="H45" s="1">
+        <v>0</v>
       </c>
       <c r="I45" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J45" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" ht="16.5" spans="1:10">
+      <c r="K45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:11">
       <c r="A46" s="1">
         <f t="shared" si="0"/>
         <v>2005010</v>
@@ -2806,10 +2967,10 @@
         <v>200500</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E46" s="10">
         <v>10</v>
@@ -2820,17 +2981,20 @@
       <c r="G46" s="10">
         <v>-1</v>
       </c>
-      <c r="H46" s="10">
-        <v>50</v>
+      <c r="H46" s="1">
+        <v>0</v>
       </c>
       <c r="I46" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J46" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" ht="16.5" spans="1:10">
+      <c r="K46">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="1:11">
       <c r="A47" s="1">
         <f t="shared" si="0"/>
         <v>2006010</v>
@@ -2839,10 +3003,10 @@
         <v>200600</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E47" s="10">
         <v>10</v>
@@ -2853,17 +3017,20 @@
       <c r="G47" s="10">
         <v>-1</v>
       </c>
-      <c r="H47" s="10">
-        <v>1</v>
+      <c r="H47" s="1">
+        <v>0</v>
       </c>
       <c r="I47" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J47" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" ht="16.5" spans="1:10">
+      <c r="K47">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="1:11">
       <c r="A48" s="1">
         <f t="shared" si="0"/>
         <v>2007010</v>
@@ -2872,10 +3039,10 @@
         <v>200700</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E48" s="10">
         <v>10</v>
@@ -2886,17 +3053,20 @@
       <c r="G48" s="10">
         <v>-1</v>
       </c>
-      <c r="H48" s="10">
-        <v>30</v>
+      <c r="H48" s="1">
+        <v>0</v>
       </c>
       <c r="I48" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J48" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" ht="16.5" spans="1:10">
+      <c r="K48">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="1:11">
       <c r="A49" s="1">
         <f t="shared" si="0"/>
         <v>2008010</v>
@@ -2905,10 +3075,10 @@
         <v>200800</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E49" s="10">
         <v>10</v>
@@ -2919,17 +3089,20 @@
       <c r="G49" s="10">
         <v>-1</v>
       </c>
-      <c r="H49" s="10">
-        <v>50</v>
+      <c r="H49" s="1">
+        <v>0</v>
       </c>
       <c r="I49" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J49" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" ht="16.5" spans="1:10">
+      <c r="K49">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:11">
       <c r="A50" s="1">
         <f t="shared" si="0"/>
         <v>2009010</v>
@@ -2938,10 +3111,10 @@
         <v>200900</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E50" s="10">
         <v>10</v>
@@ -2952,17 +3125,20 @@
       <c r="G50" s="10">
         <v>-1</v>
       </c>
-      <c r="H50" s="10">
-        <v>50</v>
+      <c r="H50" s="1">
+        <v>0</v>
       </c>
       <c r="I50" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J50" s="10">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" ht="16.5" spans="1:10">
+      <c r="K50">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:11">
       <c r="A51" s="1">
         <f t="shared" si="0"/>
         <v>2010010</v>
@@ -2971,10 +3147,10 @@
         <v>201000</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E51" s="10">
         <v>10</v>
@@ -2985,14 +3161,17 @@
       <c r="G51" s="10">
         <v>-1</v>
       </c>
-      <c r="H51" s="10">
-        <v>50</v>
+      <c r="H51" s="1">
+        <v>0</v>
       </c>
       <c r="I51" s="10" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J51" s="10">
         <v>1</v>
+      </c>
+      <c r="K51">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
